--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0149.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0149.xlsx
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tôi sẽ suy nghĩ về chuyện đó.</t>
+          <t>Ta sẽ suy nghĩ về chuyện này.</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta thấy thoải mái hơn một chút rồi.</t>
+          <t>Tao thấy thoải mái hơn một chút rồi.</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Nghe như ta đang làm phiền gì đó rồi.</t>
+          <t>Nghe như tao đang làm phiền gì đó rồi.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Không. Không hẳn. Nhưng ta rất vui khi gặp lại cậu ở đây.</t>
+          <t>Không. Không hẳn. Nhưng tao rất vui khi gặp lại cậu ở đây.</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Cậu nghĩ mình đã không cố hết sức à?</t>
+          <t>Mày nghĩ mình đã không cố hết sức à?</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>...Được rồi. Ta phải học hỏi tinh thần "có thể làm" của ngươi mới được!</t>
+          <t>...Được rồi. Tao phải học hỏi tinh thần "có thể làm" của mày mới được!</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Đúng rồi, ta là dân chuyên nghiệp mà!</t>
+          <t>Đúng rồi, tao là dân chuyên nghiệp mà!</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Ừ, dù sao ta cũng định thử chơi rồi. Chỉ là hơi chần chừ tí thôi.</t>
+          <t>Ừ, dù sao tao cũng định thử chơi rồi. Chỉ là hơi chần chừ tí thôi.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Đó là điều ta thấy thú vị ở "Stellar Orbit Beats."</t>
+          <t>Đó là điều tao thấy thú vị ở "Stellar Orbit Beats."</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17214,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Tập thể Spacetrek sẽ mãi tôn vinh sự cống hiến của bạn!</t>
+          <t>Hội Tập Đoàn Spacetrek sẽ mãi tôn vinh công lao của ngươi!</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Chuyện đó ta không nên nói đâu. Ta nhắn cho ngươi chỉ để gửi tấm ảnh này thôi.</t>
+          <t>Chuyện đó tao không nên nói đâu. Tao nhắn cho mày chỉ để gửi tấm ảnh này thôi.</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Ta tin nguyên nhân của cảnh tượng này có liên quan đến cường độ bức xạ mặt trời, phải không?</t>
+          <t>Tao tin nguyên nhân của cảnh tượng này có liên quan đến cường độ bức xạ mặt trời, phải không?</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Ủa?</t>
+          <t>Ờ?</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ảnh: Rover tại Học Viện với Lò Phản Ứng phía sau.</t>
+          <t>Ảnh: Rover at the Academy with the Reactor Drive in the background.</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Hiếm lắm mới nghe thứ ta không hiểu nổi. Thôi, quay lại với cây đàn đi.</t>
+          <t>Hiếm lắm mới nghe thứ tao không hiểu nổi. Thôi, quay lại với cây đàn đi.</t>
         </is>
       </c>
     </row>
@@ -23844,7 +23844,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>(ゝ∀･) Ta sẽ nhớ lời đó đấy! Để ta lên kế hoạch lộ trình ngay!</t>
+          <t>(ゝ∀･) Tao sẽ nhớ lời đó đấy! Để tao lên kế hoạch lộ trình ngay!</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Nhưng giờ ta đã nóng lòng muốn được cưỡi xe rồi...</t>
+          <t>Nhưng giờ tao đã nóng lòng muốn được cưỡi xe rồi...</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>(ゝ∀･) Ta biết ngay là tụi mình sẽ vui lắm đây! Giờ chỉ cần đợi trời quang thôi.</t>
+          <t>(ゝ∀･) Tao biết ngay là tụi mình sẽ vui lắm đây! Giờ chỉ cần đợi trời quang thôi.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Arsenio á? Cậu đang nói cái gì vậy?</t>
+          <t>Arsenio á? Mày đang nói cái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -26184,7 +26184,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Hồi còn ở Rừng Bjartr, lũ trẻ Roya không hiểu nổi cách ta nói chuyện.</t>
+          <t>Hồi còn ở Bjartr Woods, lũ trẻ Roya không hiểu nổi cách ta nói chuyện.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Hello.</t>
+          <t>Xin chào.</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Lynae kể cậu đã gỡ bỏ hóa đá cho Jetray như thế nào. Đúng là Rover mà tớ biết.</t>
+          <t>Lynae kể cậu đã gỡ bỏ hóa đá cho Jetray như thế nào. Đúng là Vận Mệnh Giả mà tớ biết.</t>
         </is>
       </c>
     </row>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Nếu ta bảo không muốn nghe, ngươi có giận không?</t>
+          <t>Nếu tao bảo không muốn nghe, mày có giận không?</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Cậu chẳng tỏ ra sợ hãi gì cả. Có vẻ lần sau ta phải bịa chuyện gì đáng tin hơn mới được.</t>
+          <t>Cậu chẳng tỏ ra sợ hãi gì cả. Có vẻ lần sau tao phải bịa chuyện gì đáng tin hơn mới được.</t>
         </is>
       </c>
     </row>
